--- a/docs/workbook.xlsx
+++ b/docs/workbook.xlsx
@@ -799,7 +799,7 @@
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>Amount, the account it was paid from, and what it was for. Optionally category, subcategory, budget group, date.</t>
+          <t>Amount, the account it was paid from, and what it was for. Optionally category, subcategory, budget group, date, note.</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
@@ -811,7 +811,7 @@
 Categories are exactly two levels deep - category and subcategory, no further nesting (confirmed). Category and budget are independent axes: transportation can belong to travel or to work.
 Constraint (FR-17): spending with no budget group appears under "Others" in the budget view rather than escaping it.
 Constraint (NFR-1): usability outranks accounting correctness - no ceremony on the common path.
-Open (fr-nfr.md section 4): whether a transaction carries a free-text note was never actually stated - "amount, what it was for" may have meant the category alone.</t>
+Decided (fr-nfr.md, 2026-08-21): a transaction carries an optional, nullable free-text note - offered here alongside the tags, never required, and not read by the app to make any decision.</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>Amount, the account it went into, and what it was. Optionally category, subcategory, budget group, date.</t>
+          <t>Amount, the account it went into, and what it was. Optionally category, subcategory, budget group, date, note.</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>Source account, destination account, amount, date.</t>
+          <t>Source account, destination account, amount, date. Optionally a free-text note.</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
@@ -940,7 +940,7 @@
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>Which person or debt it concerns, the direction (I lent / I borrowed), the amount, and the account the money moved through.</t>
+          <t>Which person or debt it concerns, the direction (I lent / I borrowed), the amount, and the account the money moved through. Optionally a free-text note.</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>Which debt or person, the direction of the repayment, the amount, and the account it moved through.</t>
+          <t>Which debt or person, the direction of the repayment, the amount, and the account it moved through. Optionally a free-text note.</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
@@ -1042,7 +1042,7 @@
 2. Owner amends any of it - amount, account, date, category, subcategory, budget group - or deletes it outright.
 3. System re-derives every affected figure: account amounts, the balance-sheet totals, and budget consumption.
 Applies to every kind of transaction: expense, income, transfer, lending, borrowing, repayment, adjustment.
-Ruling (fr-nfr.md section 3): editing a transaction does not conflict with a month's report staying faithful. A budget is a commitment made in advance, so it locks (FR-16); a transaction is a record of what happened, so it stays correctable. Tidying one's own records is the owner's business, not the app's.
+Ruling (fr-nfr.md section 3): editing a transaction does not conflict with a month's report staying faithful. A transaction is a record of what happened, so it stays correctable - the owner's FR-18 ruling (2026-08-19) gives transactions their own dedicated correction use case (this one), plus UC-03 for accounts; everywhere else, edit and delete are alternate flows of the use case that creates the record. Tidying one's own records is the owner's business, not the app's.
 Constraint (NFR-2): nothing stored needs fixing up afterwards, because balances were never stored.
 Constraint (NFR-4): the app assists, it does not police - a correction touching an already-closed month is allowed.
 This is the only entity with its own correction use case (owner's decision, 2026-08-19); for every other entity, edit and delete are alternate flows of the use case that creates it.</t>
@@ -1129,15 +1129,16 @@
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>The month, each budget group, and the amount for it (pre-filled from the previous month).</t>
+          <t>The month, each budget group, and the amount for it (pre-filled from the previous month). To create, rename, or delete a budget group: the group name.</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
           <t>FR-12: "I can set a monthly amount for a budget group." FR-15: "Next month's budget is set automatically from this month's, and I can change it." FR-16 (rewritten 2026-08-20): "I can change a month's budget at any time, including after the month has started."
-1. System pre-fills the new month's amounts from the previous month's, automatically, so setting a budget does not become a monthly chore that gets skipped.
-2. Owner changes any amount they want to, because months differ.
-3. The amount stays editable for the whole life of the period, and the period can also be deleted. There is no lock and no point at which a change is refused (FR-18, NFR-4).
+1. Owner creates, renames, or deletes a budget group as needed - groups are managed here since a budget amount is always set against one (owner's ruling, 2026-08-21: moved from UC-13, which has no supporting screen for it; this use case already owns Budget_Group via SetBudgetScreen / BudgetNotifier / BudgetDao).
+2. System pre-fills the new month's amounts from the previous month's, automatically, so setting a budget does not become a monthly chore that gets skipped.
+3. Owner changes any amount they want to, because months differ.
+4. The amount stays editable for the whole life of the period, and the period can also be deleted. There is no lock and no point at which a change is refused (FR-18, NFR-4).
 Constraint (FR-12): a budget is a soft limit on spending, not an enforced one - going over is recorded, not prevented.
 Constraint (FR-14): each month's budget stands alone and unspent money does not carry forward. Accounts run continuously; budgets do not. The reason is report fidelity - a month's numbers reflect that month and nothing else. This is unaffected by the lock removal; it is about carry-forward, not about editability.
 Accepted cost (FR-16, 2026-08-20): the lock previously refused a week-three change, and its purpose was report fidelity rather than discipline - a report measured against a moving target says nothing. Without it, the spent-vs-budget comparison in UC-12 is always satisfiable after the fact, because nothing distinguishes an amount set in advance from one raised later to match what was spent. The owner was told this and chose it deliberately: "it's about users discipline anyways".
@@ -1148,7 +1149,7 @@
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>Each budget group has an amount for that month, editable during the first week and locked thereafter.</t>
+          <t>Budget groups exist (created, renamed, or deleted as needed), and each has an amount for that month that stays editable for the whole life of the period - no lock, no lifecycle, and no point at which a change is refused (FR-16 rewritten 2026-08-20, ISSUE-004).</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
@@ -1212,7 +1213,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Set Up Categories and Budget Groups</t>
+          <t>Set Up Categories and Subcategories</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -1227,7 +1228,7 @@
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>Category names, subcategory names and the category each belongs under, and budget group names.</t>
+          <t>Category names, and subcategory names and the category each belongs under.</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
@@ -1235,20 +1236,19 @@
           <t>FR-10: "I can tag what I record with a category, a subcategory, and a budget group, and any of them can be left blank." FR-18: "I can create, view, edit, and delete everything I record."
 1. Owner defines the categories they want to tag things with.
 2. Owner adds subcategories under a category. Exactly two levels - category and subcategory, no further nesting (confirmed).
-3. Owner defines budget groups separately. These are an independent axis, not a level of the category tree: transportation can belong to travel or to work.
-4. All of these are available, and all optional, whenever the owner records something.
-Alternate flows: renaming and deleting a category, subcategory, or budget group are alternate flows of this use case (owner's decision, 2026-08-19: only transactions get their own correction use case).
-Setting the monthly amount against a budget group is a different use case - UC-11.</t>
+3. Both are available, and both optional, whenever the owner records something.
+Alternate flows: renaming and deleting a category or subcategory are alternate flows of this use case (owner's decision, 2026-08-19: only transactions get their own correction use case).
+Budget groups - creating, renaming, deleting, and setting their monthly amount - are handled by UC-11, which owns the Budget_Group entity (owner's ruling, 2026-08-21: moved out of this use case because the screen that would have managed a budget group here has no supporting class on any diagram, while UC-11's SetBudgetScreen / BudgetNotifier / BudgetDao already do).</t>
         </is>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>Category, subcategory, and budget group lists exist and are offered when recording a transaction.</t>
+          <t>Category and subcategory lists exist and are offered when recording a transaction.</t>
         </is>
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
-          <t>Category, Subcategory, Budget_Group</t>
+          <t>Category, Subcategory</t>
         </is>
       </c>
     </row>

--- a/docs/workbook.xlsx
+++ b/docs/workbook.xlsx
@@ -1144,7 +1144,7 @@
 Accepted cost (FR-16, 2026-08-20): the lock previously refused a week-three change, and its purpose was report fidelity rather than discipline - a report measured against a moving target says nothing. Without it, the spent-vs-budget comparison in UC-12 is always satisfiable after the fact, because nothing distinguishes an amount set in advance from one raised later to match what was spent. The owner was told this and chose it deliberately: "it's about users discipline anyways".
 Budgets are their own thing - not accounts, not categories. They behave like an account in that they hold an amount that drains as it is used, but they are a separate table alongside accounts and categories.
 Note: this use case previously carried the app's only lifecycle (open -&gt; locked -&gt; closed). Removing the lock collapsed it - "locked" ceased to exist and the rest is a date comparison that restricts nothing - so Budget_Period now has no state diagram. See docs/statuses.md.
-Open (fr-nfr.md section 4): what "a month" means - calendar month or payday-to-payday - was never discussed; calendar was assumed throughout. Also deferred to the ERD: whether a budget's identity is separate from its monthly amount.</t>
+Both questions this row once listed as open are now decided, and UC-11 was built on both (2026-08-22). What "a month" means: the calendar month, decided 2026-08-20 - payday-to-payday was rejected because a period boundary would then derive from an editable transaction, and FR-18 makes every transaction editable. Whether a budget's identity is separate from its monthly amount: yes, settled at the ERD - ISSUE-001 split it into Budget_Group and Budget_Period, which is why Entity/Objek Terkait on this row names both. See context/index/decisions.md for both.</t>
         </is>
       </c>
       <c r="G12" s="7" t="inlineStr">
